--- a/full_eval_v2.xlsx
+++ b/full_eval_v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="210">
   <si>
     <t>index</t>
   </si>
@@ -1057,10 +1057,10 @@
         <v>206</v>
       </c>
       <c r="K2">
-        <v>22711</v>
+        <v>1287</v>
       </c>
       <c r="L2">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1098,10 +1098,10 @@
         <v>207</v>
       </c>
       <c r="K3">
-        <v>7049</v>
+        <v>1624</v>
       </c>
       <c r="L3">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>206</v>
       </c>
       <c r="K4">
-        <v>6942</v>
+        <v>1540</v>
       </c>
       <c r="L4">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -1180,10 +1180,10 @@
         <v>207</v>
       </c>
       <c r="K5">
-        <v>3656</v>
+        <v>1745</v>
       </c>
       <c r="L5">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -1221,10 +1221,10 @@
         <v>207</v>
       </c>
       <c r="K6">
-        <v>4863</v>
+        <v>1649</v>
       </c>
       <c r="L6">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1262,10 +1262,10 @@
         <v>206</v>
       </c>
       <c r="K7">
-        <v>5630</v>
+        <v>1268</v>
       </c>
       <c r="L7">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -1303,10 +1303,10 @@
         <v>206</v>
       </c>
       <c r="K8">
-        <v>4757</v>
+        <v>2040</v>
       </c>
       <c r="L8">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1344,10 +1344,10 @@
         <v>206</v>
       </c>
       <c r="K9">
-        <v>746</v>
+        <v>1319</v>
       </c>
       <c r="L9">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1385,10 +1385,10 @@
         <v>208</v>
       </c>
       <c r="K10">
-        <v>6169</v>
+        <v>1350</v>
       </c>
       <c r="L10">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -1426,10 +1426,10 @@
         <v>207</v>
       </c>
       <c r="K11">
-        <v>4336</v>
+        <v>3410</v>
       </c>
       <c r="L11">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -1467,10 +1467,10 @@
         <v>206</v>
       </c>
       <c r="K12">
-        <v>5555</v>
+        <v>1671</v>
       </c>
       <c r="L12">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -1508,10 +1508,10 @@
         <v>206</v>
       </c>
       <c r="K13">
-        <v>696</v>
+        <v>1784</v>
       </c>
       <c r="L13">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -1549,10 +1549,10 @@
         <v>207</v>
       </c>
       <c r="K14">
-        <v>7502</v>
+        <v>1665</v>
       </c>
       <c r="L14">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -1590,10 +1590,10 @@
         <v>208</v>
       </c>
       <c r="K15">
-        <v>4435</v>
+        <v>1829</v>
       </c>
       <c r="L15">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1631,10 +1631,10 @@
         <v>206</v>
       </c>
       <c r="K16">
-        <v>1156</v>
+        <v>3263</v>
       </c>
       <c r="L16">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -1672,10 +1672,10 @@
         <v>206</v>
       </c>
       <c r="K17">
-        <v>6568</v>
+        <v>1897</v>
       </c>
       <c r="L17">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1713,10 +1713,10 @@
         <v>208</v>
       </c>
       <c r="K18">
-        <v>5798</v>
+        <v>1555</v>
       </c>
       <c r="L18">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -1754,10 +1754,10 @@
         <v>209</v>
       </c>
       <c r="K19">
-        <v>402</v>
+        <v>5960</v>
       </c>
       <c r="L19">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1795,10 +1795,10 @@
         <v>209</v>
       </c>
       <c r="K20">
-        <v>6965</v>
+        <v>1309</v>
       </c>
       <c r="L20">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -1836,10 +1836,10 @@
         <v>209</v>
       </c>
       <c r="K21">
-        <v>1138</v>
+        <v>1318</v>
       </c>
       <c r="L21">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -1859,25 +1859,28 @@
         <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="s">
         <v>193</v>
       </c>
+      <c r="H22" t="s">
+        <v>193</v>
+      </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="s">
         <v>209</v>
       </c>
       <c r="K22">
-        <v>8548</v>
+        <v>1526</v>
       </c>
       <c r="L22">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -1915,10 +1918,10 @@
         <v>209</v>
       </c>
       <c r="K23">
-        <v>2817</v>
+        <v>1992</v>
       </c>
       <c r="L23">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -1938,25 +1941,28 @@
         <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="s">
         <v>194</v>
       </c>
+      <c r="H24" t="s">
+        <v>194</v>
+      </c>
       <c r="I24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="s">
         <v>208</v>
       </c>
       <c r="K24">
-        <v>3555</v>
+        <v>2414</v>
       </c>
       <c r="L24">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="M24" t="b">
         <v>1</v>
@@ -1976,14 +1982,17 @@
         <v>187</v>
       </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
         <v>194</v>
       </c>
+      <c r="H25" t="s">
+        <v>195</v>
+      </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
@@ -1991,10 +2000,10 @@
         <v>206</v>
       </c>
       <c r="K25">
-        <v>891</v>
+        <v>1710</v>
       </c>
       <c r="L25">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -2014,25 +2023,28 @@
         <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="s">
         <v>194</v>
       </c>
+      <c r="H26" t="s">
+        <v>194</v>
+      </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="s">
         <v>208</v>
       </c>
       <c r="K26">
-        <v>5892</v>
+        <v>2058</v>
       </c>
       <c r="L26">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="M26" t="b">
         <v>1</v>
@@ -2052,25 +2064,28 @@
         <v>187</v>
       </c>
       <c r="E27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>194</v>
       </c>
+      <c r="H27" t="s">
+        <v>194</v>
+      </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="s">
         <v>209</v>
       </c>
       <c r="K27">
-        <v>2899</v>
+        <v>1665</v>
       </c>
       <c r="L27">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -2108,10 +2123,10 @@
         <v>208</v>
       </c>
       <c r="K28">
-        <v>12101</v>
+        <v>1706</v>
       </c>
       <c r="L28">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M28" t="b">
         <v>1</v>
@@ -2149,10 +2164,10 @@
         <v>206</v>
       </c>
       <c r="K29">
-        <v>3597</v>
+        <v>2499</v>
       </c>
       <c r="L29">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -2190,10 +2205,10 @@
         <v>209</v>
       </c>
       <c r="K30">
-        <v>6424</v>
+        <v>2173</v>
       </c>
       <c r="L30">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M30" t="b">
         <v>1</v>
@@ -2231,10 +2246,10 @@
         <v>208</v>
       </c>
       <c r="K31">
-        <v>405</v>
+        <v>2589</v>
       </c>
       <c r="L31">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="M31" t="b">
         <v>1</v>
@@ -2272,10 +2287,10 @@
         <v>206</v>
       </c>
       <c r="K32">
-        <v>317</v>
+        <v>1393</v>
       </c>
       <c r="L32">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -2313,10 +2328,10 @@
         <v>208</v>
       </c>
       <c r="K33">
-        <v>546</v>
+        <v>2025</v>
       </c>
       <c r="L33">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="M33" t="b">
         <v>1</v>
@@ -2354,10 +2369,10 @@
         <v>209</v>
       </c>
       <c r="K34">
-        <v>7215</v>
+        <v>2259</v>
       </c>
       <c r="L34">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
@@ -2377,7 +2392,7 @@
         <v>188</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -2385,17 +2400,20 @@
       <c r="G35" t="s">
         <v>196</v>
       </c>
+      <c r="H35" t="s">
+        <v>196</v>
+      </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="s">
         <v>209</v>
       </c>
       <c r="K35">
-        <v>5797</v>
+        <v>1823</v>
       </c>
       <c r="L35">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="M35" t="b">
         <v>1</v>
@@ -2433,10 +2451,10 @@
         <v>209</v>
       </c>
       <c r="K36">
-        <v>6481</v>
+        <v>3857</v>
       </c>
       <c r="L36">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M36" t="b">
         <v>1</v>
@@ -2474,10 +2492,10 @@
         <v>209</v>
       </c>
       <c r="K37">
-        <v>23165</v>
+        <v>2528</v>
       </c>
       <c r="L37">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M37" t="b">
         <v>1</v>
@@ -2512,10 +2530,10 @@
         <v>209</v>
       </c>
       <c r="K38">
-        <v>5582</v>
+        <v>2185</v>
       </c>
       <c r="L38">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="M38" t="b">
         <v>1</v>
@@ -2553,10 +2571,10 @@
         <v>209</v>
       </c>
       <c r="K39">
-        <v>968</v>
+        <v>1472</v>
       </c>
       <c r="L39">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -2594,10 +2612,10 @@
         <v>209</v>
       </c>
       <c r="K40">
-        <v>410</v>
+        <v>1733</v>
       </c>
       <c r="L40">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="M40" t="b">
         <v>1</v>
@@ -2635,10 +2653,10 @@
         <v>209</v>
       </c>
       <c r="K41">
-        <v>263</v>
+        <v>1500</v>
       </c>
       <c r="L41">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
@@ -2676,10 +2694,10 @@
         <v>209</v>
       </c>
       <c r="K42">
-        <v>279</v>
+        <v>1752</v>
       </c>
       <c r="L42">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
@@ -2714,10 +2732,10 @@
         <v>209</v>
       </c>
       <c r="K43">
-        <v>7774</v>
+        <v>2218</v>
       </c>
       <c r="L43">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
@@ -2752,10 +2770,10 @@
         <v>209</v>
       </c>
       <c r="K44">
-        <v>5754</v>
+        <v>1981</v>
       </c>
       <c r="L44">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="M44" t="b">
         <v>1</v>
@@ -2790,10 +2808,10 @@
         <v>209</v>
       </c>
       <c r="K45">
-        <v>4859</v>
+        <v>2655</v>
       </c>
       <c r="L45">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="M45" t="b">
         <v>1</v>
@@ -2828,10 +2846,10 @@
         <v>209</v>
       </c>
       <c r="K46">
-        <v>1032</v>
+        <v>2014</v>
       </c>
       <c r="L46">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="M46" t="b">
         <v>1</v>
@@ -2869,10 +2887,10 @@
         <v>209</v>
       </c>
       <c r="K47">
-        <v>632</v>
+        <v>1669</v>
       </c>
       <c r="L47">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -2910,10 +2928,10 @@
         <v>209</v>
       </c>
       <c r="K48">
-        <v>6576</v>
+        <v>3601</v>
       </c>
       <c r="L48">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
@@ -2933,7 +2951,7 @@
         <v>188</v>
       </c>
       <c r="E49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -2941,20 +2959,17 @@
       <c r="G49" t="s">
         <v>199</v>
       </c>
-      <c r="H49" t="s">
-        <v>199</v>
-      </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="s">
         <v>209</v>
       </c>
       <c r="K49">
-        <v>15718</v>
+        <v>9178</v>
       </c>
       <c r="L49">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
@@ -2974,7 +2989,7 @@
         <v>188</v>
       </c>
       <c r="E50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -2982,20 +2997,17 @@
       <c r="G50" t="s">
         <v>199</v>
       </c>
-      <c r="H50" t="s">
-        <v>199</v>
-      </c>
       <c r="I50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="s">
         <v>209</v>
       </c>
       <c r="K50">
-        <v>10207</v>
+        <v>2485</v>
       </c>
       <c r="L50">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
@@ -3033,10 +3045,10 @@
         <v>206</v>
       </c>
       <c r="K51">
-        <v>1855</v>
+        <v>31188</v>
       </c>
       <c r="L51">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
@@ -3071,10 +3083,10 @@
         <v>208</v>
       </c>
       <c r="K52">
-        <v>10412</v>
+        <v>1933</v>
       </c>
       <c r="L52">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M52" t="b">
         <v>1</v>
@@ -3112,10 +3124,10 @@
         <v>206</v>
       </c>
       <c r="K53">
-        <v>1667</v>
+        <v>2208</v>
       </c>
       <c r="L53">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
@@ -3153,10 +3165,10 @@
         <v>208</v>
       </c>
       <c r="K54">
-        <v>10476</v>
+        <v>1432</v>
       </c>
       <c r="L54">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
@@ -3194,10 +3206,10 @@
         <v>206</v>
       </c>
       <c r="K55">
-        <v>3128</v>
+        <v>4468</v>
       </c>
       <c r="L55">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
@@ -3217,28 +3229,28 @@
         <v>189</v>
       </c>
       <c r="E56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="s">
         <v>201</v>
       </c>
       <c r="H56" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="s">
         <v>206</v>
       </c>
       <c r="K56">
-        <v>4600</v>
+        <v>2277</v>
       </c>
       <c r="L56">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
@@ -3276,10 +3288,10 @@
         <v>208</v>
       </c>
       <c r="K57">
-        <v>4001</v>
+        <v>1554</v>
       </c>
       <c r="L57">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -3317,10 +3329,10 @@
         <v>206</v>
       </c>
       <c r="K58">
-        <v>6243</v>
+        <v>1729</v>
       </c>
       <c r="L58">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="M58" t="b">
         <v>1</v>
@@ -3358,10 +3370,10 @@
         <v>206</v>
       </c>
       <c r="K59">
-        <v>5247</v>
+        <v>1711</v>
       </c>
       <c r="L59">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -3399,10 +3411,10 @@
         <v>208</v>
       </c>
       <c r="K60">
-        <v>4197</v>
+        <v>2826</v>
       </c>
       <c r="L60">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M60" t="b">
         <v>1</v>
@@ -3440,10 +3452,10 @@
         <v>208</v>
       </c>
       <c r="K61">
-        <v>3392</v>
+        <v>2450</v>
       </c>
       <c r="L61">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="M61" t="b">
         <v>1</v>
@@ -3463,7 +3475,7 @@
         <v>189</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -3472,19 +3484,19 @@
         <v>202</v>
       </c>
       <c r="H62" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="s">
         <v>208</v>
       </c>
       <c r="K62">
-        <v>7160</v>
+        <v>2257</v>
       </c>
       <c r="L62">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M62" t="b">
         <v>1</v>
@@ -3522,10 +3534,10 @@
         <v>208</v>
       </c>
       <c r="K63">
-        <v>4442</v>
+        <v>1951</v>
       </c>
       <c r="L63">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="M63" t="b">
         <v>1</v>
@@ -3563,10 +3575,10 @@
         <v>208</v>
       </c>
       <c r="K64">
-        <v>7486</v>
+        <v>2098</v>
       </c>
       <c r="L64">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="M64" t="b">
         <v>1</v>
@@ -3604,10 +3616,10 @@
         <v>208</v>
       </c>
       <c r="K65">
-        <v>6915</v>
+        <v>2246</v>
       </c>
       <c r="L65">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
@@ -3645,10 +3657,10 @@
         <v>208</v>
       </c>
       <c r="K66">
-        <v>17997</v>
+        <v>3221</v>
       </c>
       <c r="L66">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M66" t="b">
         <v>1</v>
@@ -3683,10 +3695,10 @@
         <v>208</v>
       </c>
       <c r="K67">
-        <v>5357</v>
+        <v>2245</v>
       </c>
       <c r="L67">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
@@ -3724,10 +3736,10 @@
         <v>208</v>
       </c>
       <c r="K68">
-        <v>13061</v>
+        <v>2400</v>
       </c>
       <c r="L68">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -3762,10 +3774,10 @@
         <v>209</v>
       </c>
       <c r="K69">
-        <v>2636</v>
+        <v>3159</v>
       </c>
       <c r="L69">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -3785,28 +3797,28 @@
         <v>189</v>
       </c>
       <c r="E70" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="s">
         <v>204</v>
       </c>
       <c r="H70" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="s">
         <v>208</v>
       </c>
       <c r="K70">
-        <v>790</v>
+        <v>2254</v>
       </c>
       <c r="L70">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -3844,10 +3856,10 @@
         <v>208</v>
       </c>
       <c r="K71">
-        <v>12850</v>
+        <v>3444</v>
       </c>
       <c r="L71">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="M71" t="b">
         <v>1</v>
@@ -3882,10 +3894,10 @@
         <v>206</v>
       </c>
       <c r="K72">
-        <v>11162</v>
+        <v>3193</v>
       </c>
       <c r="L72">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M72" t="b">
         <v>1</v>
@@ -3905,28 +3917,28 @@
         <v>189</v>
       </c>
       <c r="E73" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="s">
         <v>204</v>
       </c>
       <c r="H73" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="s">
         <v>208</v>
       </c>
       <c r="K73">
-        <v>4149</v>
+        <v>3792</v>
       </c>
       <c r="L73">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M73" t="b">
         <v>1</v>
@@ -3961,10 +3973,10 @@
         <v>208</v>
       </c>
       <c r="K74">
-        <v>5064</v>
+        <v>4788</v>
       </c>
       <c r="L74">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
@@ -4002,10 +4014,10 @@
         <v>208</v>
       </c>
       <c r="K75">
-        <v>15496</v>
+        <v>3160</v>
       </c>
       <c r="L75">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M75" t="b">
         <v>1</v>
@@ -4025,17 +4037,14 @@
         <v>189</v>
       </c>
       <c r="E76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="s">
         <v>205</v>
       </c>
-      <c r="H76" t="s">
-        <v>195</v>
-      </c>
       <c r="I76" t="b">
         <v>0</v>
       </c>
@@ -4043,10 +4052,10 @@
         <v>206</v>
       </c>
       <c r="K76">
-        <v>7664</v>
+        <v>2602</v>
       </c>
       <c r="L76">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="M76" t="b">
         <v>1</v>
@@ -4066,28 +4075,28 @@
         <v>189</v>
       </c>
       <c r="E77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="s">
         <v>205</v>
       </c>
       <c r="H77" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="s">
         <v>206</v>
       </c>
       <c r="K77">
-        <v>15289</v>
+        <v>2183</v>
       </c>
       <c r="L77">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="M77" t="b">
         <v>1</v>
@@ -4119,10 +4128,10 @@
         <v>209</v>
       </c>
       <c r="K78">
-        <v>10436</v>
+        <v>4769</v>
       </c>
       <c r="L78">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="M78" t="b">
         <v>1</v>
@@ -4154,10 +4163,10 @@
         <v>209</v>
       </c>
       <c r="K79">
-        <v>13485</v>
+        <v>1936</v>
       </c>
       <c r="L79">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M79" t="b">
         <v>1</v>
@@ -4189,10 +4198,10 @@
         <v>209</v>
       </c>
       <c r="K80">
-        <v>7393</v>
+        <v>1609</v>
       </c>
       <c r="L80">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="M80" t="b">
         <v>1</v>
@@ -4230,10 +4239,10 @@
         <v>206</v>
       </c>
       <c r="K81">
-        <v>8069</v>
+        <v>2281</v>
       </c>
       <c r="L81">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
@@ -4265,10 +4274,10 @@
         <v>209</v>
       </c>
       <c r="K82">
-        <v>11744</v>
+        <v>1408</v>
       </c>
       <c r="L82">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M82" t="b">
         <v>1</v>
@@ -4303,10 +4312,10 @@
         <v>209</v>
       </c>
       <c r="K83">
-        <v>6540</v>
+        <v>2270</v>
       </c>
       <c r="L83">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -4338,10 +4347,10 @@
         <v>209</v>
       </c>
       <c r="K84">
-        <v>613</v>
+        <v>2503</v>
       </c>
       <c r="L84">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
@@ -4373,10 +4382,10 @@
         <v>209</v>
       </c>
       <c r="K85">
-        <v>5033</v>
+        <v>2174</v>
       </c>
       <c r="L85">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
@@ -4408,10 +4417,10 @@
         <v>209</v>
       </c>
       <c r="K86">
-        <v>5152</v>
+        <v>1965</v>
       </c>
       <c r="L86">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="M86" t="b">
         <v>1</v>
@@ -4446,10 +4455,10 @@
         <v>209</v>
       </c>
       <c r="K87">
-        <v>8253</v>
+        <v>2182</v>
       </c>
       <c r="L87">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
